--- a/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-01T13:19:09+00:00</t>
+    <t>2025-09-02T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -660,7 +660,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-document)</t>
+Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-combinaison-document)</t>
   </si>
   <si>
     <t>What was administered</t>
@@ -1060,7 +1060,7 @@
 </t>
   </si>
   <si>
-    <t>FR Sequence</t>
+    <t>Fr Sequence</t>
   </si>
   <si>
     <t>Dosages progressifs et fractionnés</t>
@@ -1568,7 +1568,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="86.35546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="166.42578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
